--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486449_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486449_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8335</v>
+        <v>8.1218</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5634</v>
+        <v>6.1907</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2701</v>
+        <v>1.9311</v>
       </c>
       <c r="G2" t="n">
         <v>6.594</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0443</v>
+        <v>0.3326</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.548</v>
+        <v>0.0793</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5923</v>
+        <v>0.2532</v>
       </c>
       <c r="V2" t="n">
         <v>0.7602</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.933</v>
+        <v>8.0488</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3488</v>
+        <v>7.1563</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5843</v>
+        <v>0.8925</v>
       </c>
       <c r="G3" t="n">
         <v>5.498</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.435</v>
+        <v>0.6808</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4554</v>
+        <v>0.3521</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0204</v>
+        <v>0.3287</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. RADONCIC</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7128</v>
+        <v>5.3512</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7496</v>
+        <v>4.4587</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9633</v>
+        <v>0.8925</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4406</v>
+        <v>4.453</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9465</v>
+        <v>1.1253</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4941</v>
+        <v>3.3277</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9483</v>
+        <v>5.1942</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6279</v>
+        <v>1.0616</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3204</v>
+        <v>4.1325</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5077</v>
+        <v>-0.7412</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6814</v>
+        <v>0.0636</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1737</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>0.2175</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7295</v>
+        <v>0.6808</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1286</v>
+        <v>0.3521</v>
       </c>
       <c r="U4" t="n">
-        <v>0.601</v>
+        <v>0.3287</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>D. RADONCIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2355</v>
+        <v>4.9491</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6512</v>
+        <v>3.9551</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5843</v>
+        <v>0.9941</v>
       </c>
       <c r="G5" t="n">
-        <v>4.453</v>
+        <v>3.4406</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1253</v>
+        <v>1.9465</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3277</v>
+        <v>1.4941</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1942</v>
+        <v>3.9483</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0616</v>
+        <v>2.6279</v>
       </c>
       <c r="L5" t="n">
-        <v>4.1325</v>
+        <v>1.3204</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7412</v>
+        <v>-0.5077</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0636</v>
+        <v>-0.6814</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8048999999999999</v>
+        <v>0.1737</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.435</v>
+        <v>0.9659</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4554</v>
+        <v>0.3341</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0204</v>
+        <v>0.6318</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8014</v>
+        <v>2.444</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0545</v>
+        <v>2.3424</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2532</v>
+        <v>0.1016</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8056</v>
+        <v>0.2548</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7665</v>
+        <v>-1.1405</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0391</v>
+        <v>1.3953</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5284</v>
+        <v>2.0216</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2989</v>
+        <v>0.2039</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2295</v>
+        <v>1.8177</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2772</v>
+        <v>-1.7668</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5324</v>
+        <v>-1.3444</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8096</v>
+        <v>-0.4224</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7332</v>
+        <v>1.3192</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5262</v>
+        <v>0.3209</v>
       </c>
       <c r="U6" t="n">
-        <v>0.207</v>
+        <v>0.9983</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3338</v>
+        <v>1.8033</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6466</v>
+        <v>2.2722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6872</v>
+        <v>-0.4689</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2548</v>
+        <v>1.8056</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1405</v>
+        <v>0.7665</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3953</v>
+        <v>1.0391</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0216</v>
+        <v>1.5284</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2039</v>
+        <v>1.2989</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8177</v>
+        <v>0.2295</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7668</v>
+        <v>0.2772</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3444</v>
+        <v>-0.5324</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4224</v>
+        <v>0.8096</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>1.209</v>
+        <v>0.7351</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3749</v>
+        <v>0.7439</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5839</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.204</v>
+        <v>0.8948</v>
       </c>
       <c r="E8" t="n">
-        <v>2.106</v>
+        <v>2.4531</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.902</v>
+        <v>-1.5583</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3327</v>
+        <v>-1.3247</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8363</v>
+        <v>-2.6977</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5036</v>
+        <v>1.373</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1551</v>
+        <v>0.956</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3039</v>
+        <v>-1.4354</v>
       </c>
       <c r="L8" t="n">
-        <v>0.459</v>
+        <v>2.3914</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4878</v>
+        <v>-2.2808</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5324</v>
+        <v>-1.2624</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0446</v>
+        <v>-1.0184</v>
       </c>
       <c r="P8" t="n">
         <v>0.6525</v>
@@ -1078,28 +1078,28 @@
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0142</v>
+        <v>-0.128</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7557</v>
+        <v>0.1719</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2585</v>
+        <v>-0.2998</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.13</v>
+        <v>1.695</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3252</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2743</v>
+        <v>0.2975</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8943</v>
+        <v>1.1687</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.62</v>
+        <v>-0.8712</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3247</v>
+        <v>-0.3327</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.6977</v>
+        <v>-0.8363</v>
       </c>
       <c r="I9" t="n">
-        <v>1.373</v>
+        <v>0.5036</v>
       </c>
       <c r="J9" t="n">
-        <v>0.956</v>
+        <v>0.1551</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4354</v>
+        <v>-0.3039</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3914</v>
+        <v>0.459</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2808</v>
+        <v>-0.4878</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2624</v>
+        <v>-0.5324</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0184</v>
+        <v>0.0446</v>
       </c>
       <c r="P9" t="n">
         <v>0.6525</v>
@@ -1156,28 +1156,28 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7484</v>
+        <v>1.1077</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3869</v>
+        <v>0.8184</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3615</v>
+        <v>0.2893</v>
       </c>
       <c r="V9" t="n">
-        <v>1.695</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3698</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0439</v>
+        <v>-1.4072</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8607</v>
+        <v>0.1789</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8169</v>
+        <v>-1.5861</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0326</v>
+        <v>0.8336</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8215</v>
+        <v>-3.1506</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2112</v>
+        <v>3.9843</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4724</v>
+        <v>1.8379</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9186</v>
+        <v>-1.7393</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5538</v>
+        <v>3.5771</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4398</v>
+        <v>-1.0042</v>
       </c>
       <c r="N10" t="n">
-        <v>0.09710000000000001</v>
+        <v>-1.4114</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3426</v>
+        <v>0.4072</v>
       </c>
       <c r="P10" t="n">
-        <v>0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2487</v>
+        <v>0.1289</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6992</v>
+        <v>0.3209</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5495</v>
+        <v>-0.192</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.695</v>
+        <v>-1.4997</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X10" t="n">
         <v>-1.695</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. BRAZ</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7935</v>
+        <v>-1.4472</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1031</v>
+        <v>-1.08</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6904</v>
+        <v>-0.3672</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6396</v>
+        <v>0.6623</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0274</v>
+        <v>-2.4056</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.667</v>
+        <v>3.0679</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5741000000000001</v>
+        <v>1.6665</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0944</v>
+        <v>-0.9942</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6686</v>
+        <v>2.6608</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0654</v>
+        <v>-1.0042</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.067</v>
+        <v>-1.4114</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9985000000000001</v>
+        <v>0.4072</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2175</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1936</v>
+        <v>0.0433</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4711</v>
+        <v>0.3209</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2775</v>
+        <v>-0.2776</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>M. BRAZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8033</v>
+        <v>-1.9861</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0014</v>
+        <v>-0.3266</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8019</v>
+        <v>-1.6596</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8336</v>
+        <v>-1.6396</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1506</v>
+        <v>0.0274</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9843</v>
+        <v>-1.667</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8379</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7393</v>
+        <v>0.0944</v>
       </c>
       <c r="L12" t="n">
-        <v>3.5771</v>
+        <v>-0.6686</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0042</v>
+        <v>-1.0654</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4114</v>
+        <v>-0.067</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4072</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2671</v>
+        <v>0.0009</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1406</v>
+        <v>0.2476</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4077</v>
+        <v>-0.2466</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4997</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.695</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9973</v>
+        <v>-2.352</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2602</v>
+        <v>-2.9531</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7371</v>
+        <v>0.6011</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6623</v>
+        <v>-2.0326</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4056</v>
+        <v>-1.8215</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0679</v>
+        <v>-0.2112</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6665</v>
+        <v>-2.4724</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9942</v>
+        <v>-1.9186</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6608</v>
+        <v>-0.5538</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0042</v>
+        <v>0.4398</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4114</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4072</v>
+        <v>0.3426</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R13" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5069</v>
+        <v>0.9406</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1406</v>
+        <v>0.6069</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6475</v>
+        <v>0.3338</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1952</v>
+        <v>-1.695</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3904</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="14">
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>23.6903</v>
+        <v>24.718</v>
       </c>
       <c r="E14" t="n">
-        <v>24.78899999999999</v>
+        <v>25.8164</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0985</v>
+        <v>-1.0984</v>
       </c>
       <c r="G14" t="n">
         <v>18.2123</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.8729</v>
+        <v>-6.872900000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>25.0851</v>
+        <v>25.08509999999999</v>
       </c>
       <c r="J14" t="n">
         <v>26.9394</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1343000000000012</v>
+        <v>-0.134300000000001</v>
       </c>
       <c r="L14" t="n">
         <v>27.0735</v>
@@ -1531,7 +1531,7 @@
         <v>-8.727</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.738899999999999</v>
+        <v>-6.7389</v>
       </c>
       <c r="O14" t="n">
         <v>-1.9885</v>
@@ -1540,19 +1540,19 @@
         <v>3.2624</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.787700000000001</v>
+        <v>-9.787699999999999</v>
       </c>
       <c r="R14" t="n">
         <v>13.05</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7801</v>
+        <v>6.807799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6414</v>
+        <v>4.669</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1388</v>
+        <v>2.1391</v>
       </c>
       <c r="V14" t="n">
         <v>-3.5644</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7773</v>
+        <v>3.9622</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0596</v>
+        <v>5.6126</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2823</v>
+        <v>-1.6503</v>
       </c>
       <c r="G15" t="n">
         <v>3.3802</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6422</v>
+        <v>-0.4572</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0168</v>
+        <v>-0.4638</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6254</v>
+        <v>0.0066</v>
       </c>
       <c r="V15" t="n">
         <v>0.8218</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6805</v>
+        <v>0.4918</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8033</v>
+        <v>3.6916</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1228</v>
+        <v>-3.1998</v>
       </c>
       <c r="G16" t="n">
         <v>2.5592</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0055</v>
+        <v>-1.1942</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6249</v>
+        <v>-0.7366</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3806</v>
+        <v>-0.4576</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8732</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.524</v>
+        <v>0.0655</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4972</v>
+        <v>0.162</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0268</v>
+        <v>-0.0965</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1148</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6388</v>
+        <v>0.1803</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6766</v>
+        <v>0.3413</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0377</v>
+        <v>-0.161</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9961</v>
+        <v>-1.3006</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3927</v>
+        <v>-0.728</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6034</v>
+        <v>-0.5726</v>
       </c>
       <c r="G18" t="n">
         <v>0.0828</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3991</v>
+        <v>0.0946</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6766</v>
+        <v>0.3413</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2775</v>
+        <v>-0.2466</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3904</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0241</v>
+        <v>-1.483</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4715</v>
+        <v>0.5742</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4956</v>
+        <v>-2.0572</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3083</v>
+        <v>-1.0234</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1581</v>
+        <v>2.7736</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.4664</v>
+        <v>-3.797</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0539</v>
+        <v>1.2686</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8244</v>
+        <v>2.7953</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2295</v>
+        <v>-1.5267</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.3622</v>
+        <v>-2.292</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6663</v>
+        <v>-0.0217</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.6959</v>
+        <v>-2.2703</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8067</v>
+        <v>-0.2166</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4627</v>
+        <v>-0.1718</v>
       </c>
       <c r="U19" t="n">
-        <v>0.344</v>
+        <v>-0.0448</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>-0.678</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.077</v>
+        <v>-1.8227</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5341</v>
+        <v>-1.3106</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5429</v>
+        <v>-0.5121</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0976</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4145</v>
+        <v>-0.1601</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.137</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2775</v>
+        <v>-0.2466</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1072</v>
+        <v>-2.6869</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7977</v>
+        <v>0.0244</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9049</v>
+        <v>-2.7114</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0234</v>
+        <v>-3.3083</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7736</v>
+        <v>0.1581</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.797</v>
+        <v>-3.4664</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2686</v>
+        <v>1.0539</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7953</v>
+        <v>0.8244</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5267</v>
+        <v>0.2295</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.292</v>
+        <v>-4.3622</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0217</v>
+        <v>-0.6663</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.2703</v>
+        <v>-3.6959</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8408</v>
+        <v>0.1439</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0517</v>
+        <v>0.0156</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8925</v>
+        <v>0.1283</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.678</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. FILIPOVIC</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8049</v>
+        <v>-4.2769</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0157</v>
+        <v>0.5386</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7891</v>
+        <v>-4.8155</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.5446</v>
+        <v>-5.0041</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4957</v>
+        <v>-0.6995</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.0488</v>
+        <v>-4.3046</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3993</v>
+        <v>-0.0706</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1857</v>
+        <v>-0.6292</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5849</v>
+        <v>0.5587</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1453</v>
+        <v>-4.9335</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6814</v>
+        <v>-0.0703</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.4639</v>
+        <v>-4.8633</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-1.4622</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6165</v>
+        <v>-0.6056</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2963</v>
+        <v>-0.8565</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3.2769</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.3899</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>G. FILIPOVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3937</v>
+        <v>-4.458</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1309</v>
+        <v>-1.7922</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2629</v>
+        <v>-2.6658</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.393</v>
+        <v>-4.5446</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4511</v>
+        <v>-0.4957</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.8442</v>
+        <v>-4.0488</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6935</v>
+        <v>-1.3993</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7374</v>
+        <v>0.1857</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0439</v>
+        <v>-1.5849</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.0865</v>
+        <v>-3.1453</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2863</v>
+        <v>-0.6814</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.8003</v>
+        <v>-2.4639</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.0451</v>
+        <v>0.6525</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0067</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6249</v>
+        <v>-0.3929</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6316000000000001</v>
+        <v>-0.173</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0377</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1507</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4728</v>
+        <v>-4.9037</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0202</v>
+        <v>-2.8785</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.4526</v>
+        <v>-2.0253</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.0041</v>
+        <v>-4.7486</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6995</v>
+        <v>-0.2647</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.3046</v>
+        <v>-4.4839</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0706</v>
+        <v>-2.6153</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6292</v>
+        <v>-0.3618</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5587</v>
+        <v>-2.2535</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.9335</v>
+        <v>-2.1333</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0703</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.8633</v>
+        <v>-2.2304</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.658</v>
+        <v>-0.265</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1644</v>
+        <v>-0.2632</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4936</v>
+        <v>-0.0018</v>
       </c>
       <c r="V24" t="n">
-        <v>3.2769</v>
+        <v>-0.7602</v>
       </c>
       <c r="W24" t="n">
-        <v>3.3899</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.113</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7965</v>
+        <v>-5.043</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4373</v>
+        <v>-2.7956</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3592</v>
+        <v>-2.2474</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.7486</v>
+        <v>-3.393</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2647</v>
+        <v>2.4511</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.4839</v>
+        <v>-5.8442</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.6153</v>
+        <v>0.6935</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3618</v>
+        <v>2.7374</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.2535</v>
+        <v>-2.0439</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1333</v>
+        <v>-4.0865</v>
       </c>
       <c r="N25" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.2863</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.2304</v>
+        <v>-3.8003</v>
       </c>
       <c r="P25" t="n">
-        <v>0.87</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R25" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1577</v>
+        <v>0.3575</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.822</v>
+        <v>-0.2896</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3358</v>
+        <v>0.6471</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7602</v>
+        <v>1.0377</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.1507</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.7602</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="26">
@@ -2437,31 +2437,31 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-23.6905</v>
+        <v>-21.4553</v>
       </c>
       <c r="E26" t="n">
-        <v>1.098399999999999</v>
+        <v>1.098499999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-24.7889</v>
+        <v>-22.5539</v>
       </c>
       <c r="G26" t="n">
         <v>-18.2122</v>
       </c>
       <c r="H26" t="n">
-        <v>6.8731</v>
+        <v>6.873099999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-25.0851</v>
       </c>
       <c r="J26" t="n">
-        <v>8.727</v>
+        <v>8.727000000000002</v>
       </c>
       <c r="K26" t="n">
         <v>6.738700000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>1.9885</v>
+        <v>1.988499999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-26.9393</v>
@@ -2482,22 +2482,22 @@
         <v>9.7875</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.780200000000001</v>
+        <v>-3.545</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.1389</v>
+        <v>-2.1388</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.6413</v>
+        <v>-1.4059</v>
       </c>
       <c r="V26" t="n">
         <v>3.5646</v>
       </c>
       <c r="W26" t="n">
-        <v>7.5608</v>
+        <v>7.560799999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.996300000000001</v>
+        <v>-3.9963</v>
       </c>
     </row>
   </sheetData>
